--- a/task_1_2.xlsx
+++ b/task_1_2.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{708F1B3C-AE0B-4396-9D1D-B122603FE0FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B4B00A-CEA1-41C3-BDD8-B5F2F03A2B6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{213767DE-6DC6-4BD1-A726-D69F35E76078}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_pgrq54fbqmo7" localSheetId="0">Sheet1!$A$131</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="112">
   <si>
     <t>Асуулт</t>
   </si>
@@ -59,1378 +62,6 @@
     <t>A</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{42}$ тоо ямар хоёр дараалсан бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5 ба 6  B. 6 ба 7  C. 7 ба 8  D. 41 ба 43</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{320} - \sqrt{5} + \sqrt{1280}$ илэрхийллийг хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $25\sqrt{5}$  B. $21\sqrt{5}$  C. $23\sqrt{5}$  D. $19\sqrt{5}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(3^4 \cdot 3^5)^7 \div 27^{20}$ илэрхийллийн утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3  B. 9  C. 27  D. 81</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$325.78$ тоог гурван тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 325.8  B. 326.0  C. 330.0  D. 325.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.00000234$ тоог стандарт дүрсэд бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $2.34 \times 10^{-6}$  B. $23.4 \times 10^{-7}$  C. $2.34 \times 10^6$  D. $2.34 \times 10^{-5}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{11}$ тооны $0.1$ нарийвчлалтай ойролцоо утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3.3  B. 3.4  C. 3.31  D. 3.32</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(\sqrt{12} - \sqrt{75} + \sqrt{48}) \times \frac{1}{\sqrt{3}}$ үйлдлийг гүйцэтгэ. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1  B. $\sqrt{3}$  C. 3  D. $1/\sqrt{3}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\frac{7}{11}$ бутархайг аравтын бутархайд шилжүүлж, үет бутархайг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.63  B. 0.64  C. 0.(63)  D. 0.(64)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$2\sqrt{17}$ тоо ямар хоёр бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 7 ба 8  B. 8 ба 9  C. 9 ба 10  D. 16 ба 17</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$3.7 \times 10^{11} \times 9.06 \times 10^{-4}$ үйлдлийг гүйцэтгэж, стандарт дүрсээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $3.3522 \times 10^8$  B. $33.522 \times 10^7$  C. $3.35 \times 10^8$  D. $3.3522 \times 10^7$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга аль нь вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5.9  B. 6.0  C. 5.91  D. 5.92</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{128}$ илэрхийллийг $a\sqrt{b}$ дүрсэд оруул. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $4\sqrt{8}$  B. $2\sqrt{32}$  C. $8\sqrt{2}$  D. $16\sqrt{2}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$a=5.2 \times 10^7, b=4.4 \times 10^{-3}, c=3.12 \times 10^7$ тоонуудыг өсөх эрэмбээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $a, b, c$  B. $b, c, a$  C. $c, b, a$  D. $b, a, c$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\frac{\sqrt{8} - \sqrt{50} + \sqrt{32}}{\sqrt{8}}$ илэрхийллийг хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.5  B. 2  C. $2\sqrt{2}$  D. 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{30}, 6.1, 2\sqrt{10}, 4\sqrt{2}$ тоонуудыг буурах эрэмбээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $2\sqrt{10}, 6.1, 4\sqrt{2}, \sqrt{30}$  B. $6.1, 2\sqrt{10}, 4\sqrt{2}, \sqrt{30}$  C. $2\sqrt{10}, 4\sqrt{2}, 6.1, \sqrt{30}$  D. $4\sqrt{2}, 2\sqrt{10}, 6.1, \sqrt{30}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$2\sqrt{175} - 3\sqrt{28} + 2\sqrt{63}$ илэрхийллийг хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $10\sqrt{7}$  B. $12\sqrt{7}$  C. $9\sqrt{7}$  D. $11\sqrt{7}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Гэрийн шалны радиусыг метрээр тоймлоход 3 м болжээ. Талбайн хамгийн их утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $28.26$ м$^2$  B. $38.465$ м$^2$  C. $25.0$ м$^2$  D. $30.25$ м$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.00048837$ тоог нэг тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.0005  B. 0.0004  C. 0.00049  D. 0.001</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$3^{-12} \times 9^5 \div (27^{-4} \times 9^{-2})$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9  B. 81  C. 243  D. 729</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{19\frac{1}{16}}$ язгуурын утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $13/4$  B. $17/4$  C. $31/4$  D. $19/4$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{20} + \sqrt{45} - \sqrt{80}$ хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $\sqrt{5}$  B. $2\sqrt{5}$  C. $3\sqrt{5}$  D. $5\sqrt{5}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$120,000 \times 0.000002$ үржвэрийг стандарт дүрсээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $2.4 \times 10^{-1}$  B. $2.4 \times 10^{-2}$  C. $0.24$  D. $2.4 \times 10^1$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{8} + \sqrt{45}$ нийлбэрийг $0.1$ нарийвчлалтай тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.5  B. 9.4  C. 9.6  D. 9.3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$275.02 \times 10^{-3}$ утгыг аравтын бутархайгаар бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 2.7502  B. 0.27502  C. 27.502  D. 0.027502</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Тэгш өнцөгтийн урт 12 см, өргөн 7 см (см-ээр тоймлосон). Талбайн авч болох хамгийн бага утга? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 84 см$^2$  B. 74.75 см$^2$  C. 75.25 см$^2$  D. 83.25 см$^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(\sqrt{27}+1)^2$ задалж бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $28+6\sqrt{3}$  B. $28+2\sqrt{27}$  C. $29+4\sqrt{7}$  D. $29+2\sqrt{7}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{18} - 3\sqrt{8} + 2\sqrt{2}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $-\sqrt{2}$  B. $-2\sqrt{2}$  C. $\sqrt{2}$  D. 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.06754$ тоог хоёр тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.067  B. 0.068  C. 0.07  D. 0.06</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$a=3.9 \times 10^8, b=2.6 \times 10^{-5}$ бол $a \times b$ үржвэрийг стандарт дүрсэд бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.014 \times 10^2$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{90}$ тооны $0.01$ нарийвчлалтай илүүдэлтэй ойролцоо утга? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.48  B. 9.49  C. 9.5  D. 9.47</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$100 \div 10^{-3}$ утгыг 10-ын зэрэг хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^6$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{6} + \sqrt{3}$ ерөнхий үржигдэхүүн хаалтнаас гарга. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $3(\sqrt{2}+1)$  B. $\sqrt{3}(\sqrt{2}+1)$  C. $\sqrt{3}(\sqrt{2}-1)$  D. $\sqrt{2}(\sqrt{3}+1)$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$\sqrt{13^2 - 12^2}$ утгыг ол. 26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5  B. 1  C. 25  D. $\sqrt{25}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.000000000789$ тоог $7.89 \times 10^n$ хэлбэрт бичвэл $n$ хэд вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. -9  B. -10  C. -11  D. -8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{11}$ тооны $0.1$ нарийвчлалтай илүүдэлтэй ойролцоо утга? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3.3  B. 3.4  C. 3.32  D. 3.35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$5\sqrt{3} + 2\sqrt{48} - 6\sqrt{27}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $-5\sqrt{3}$  B. $-10\sqrt{3}$  C. $-2\sqrt{3}$  D. $-3\sqrt{3}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$4.3465$ тоог хоёр тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 4.3  B. 4.4  C. 4.35  D. 4.34</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(2^3)^{-2}$ утгыг 10-тын бутархайгаар бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.015625  B. 0.064  C. 0.15625  D. 0.0125</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{15} - \sqrt{10}$ ерөнхий үржигдэхүүн гарга. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $5(\sqrt{3}-\sqrt{2})$  B. $\sqrt{5}(\sqrt{3}-\sqrt{2})$  C. $\sqrt{2}(\sqrt{7.5}-1)$  D. $\sqrt{5}(3-2)$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$2^{3x} = 64$ бол $x$-ийг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1  B. 2  C. 3  D. 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{900} \div \sqrt{0.09}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 10  B. 100  C. 30  D. 300</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$1.08 \times 10^6$ тоог дэлгэрэнгүй хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1,080,000  B. 108,000  C. 10,800,000  D. 1,080,000,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{242}$ илэрхийллийг $11\sqrt{x}$ гэж бичсэн бол $x$ хэд вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 2  B. 3  C. 11  D. 22</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$29.119$ тоог $0.1$ нарийвчлалтай тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 29.1  B. 29.2  C. 29.12  D. 29.0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Гэрлийн хурд $3 \times 10^8$ м/с бол 1 минутад туулах замыг стандарт дүрсээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $1.8 \times 10^{10}$ м  B. $18 \times 10^9$ м  C. $1.8 \times 10^9$ м  D. $1.8 \times 10^{11}$ м</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{15}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3.8  B. 3.9  C. 4.0  D. 3.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(\sqrt{128} - \sqrt{32})^2$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 32  B. 64  C. 16  D. 8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.06754$ тоог нэг тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.07  B. 0.06  C. 0.1  D. 0.068</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$10^{-4}$ утгыг аравтын бутархайгаар бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.001  B. 0.0001  C. 0.00001  D. 0.1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{243} \div \sqrt{3}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9  B. 81  C. 27  D. 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$5.83 \times 10^9$ тоог дэлгэрэнгүй хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5,830,000,000 B. 583,000,000 C. 5,830,000 D. 5.83</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{75}$ илэрхийллийг $a\sqrt{b}$ хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $3\sqrt{5}$ B. $5\sqrt{3}$ C. $25\sqrt{3}$ D. $15\sqrt{5}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.000064$ тоог стандарт дүрсэд бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $6.4 \times 10^{-5}$ B. $64 \times 10^{-6}$ C. $0.64 \times 10^4$ D. $6.4 \times 10^5$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$100 \div 10^{-3}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1000 B. 10 C. 1 D. $10^5$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{90}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.5 B. 9 C. 9.4 D. 9.48</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$a=5.2 \times 10^7, b=4.4 \times 10^{-3}, c=3.12 \times 10^7$ өсөхөөр эрэмбэлсэн нь аль вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $a,b,c$ B. $b,c,a$ C. $c,b,a$ D. $b,a,c$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(\sqrt{13})^2$ илэрхийллийн утга хэд вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 13 B. -13 C. -169 D. 169</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$120,000$ тоог 10-тын зэрэг ашиглан бичнэ үү? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $12 \times 10^4$ B. $1.2 \times 10^4$ C. $12 \times 10^5$ D. $1.2 \times 10^5$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$325.78$ тоог гурван тэмдэгтээр тоймлосон нь аль нь вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 326.0 B. 330.0 C. 325.8 D. 325.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{6} + \sqrt{3}$ ерөнхий үржигдэхүүн хаалтнаас гаргаарай. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $3(2+1)$ B. $2(3+1)$ C. $\sqrt{3}(\sqrt{2}+1)$ D. $3(2-1)$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$-\sqrt{144}$ тооны язгуурын утгыг олоорой. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. -12 B. 12 C. 144 D. -144</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$11 \frac{13}{36}$ язгуурын утгыг олно уу. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $14/6$ B. $13/6$ C. $11/6$ D. $21/6$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$9^{-8} \div 9^{-9}$ илэрхийллийн утгыг олоорой. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9 B. $9^{89}$ C. 0 D. $9^{-17}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$8\sqrt{5}$ үржигдэхүүнийг язгуурын тэмдгийн дор оруулаарай. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 40 B. 320 C. $\sqrt{40}$ D. $\sqrt{320}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{32} \times \sqrt{2}$ илэрхийллийн утгыг олоорой. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $20\sqrt{2}$ B. $90\sqrt{2}$ C. 8 D. $25\sqrt{3}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга хэд вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5.9 B. 6.0 C. 5.8 D. 5.91</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$2\sqrt{17}$ ямар хоёр бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 8 ба 9 B. 7 ба 8 C. 9 ба 10 D. 2 ба 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{158^2 - 131^2}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 145 B. $15\sqrt{13}$ C. $17\sqrt{11}$ D. 289</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$7^{14} \times 7^{-12}$ илэрхийллийн утгыг олоорой. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $7^{26}$ B. $7^{-26}$ C. 7 D. 49</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.00000234$ тоог стандарт хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $2.34 \times 10^{-6}$ B. $2.34 \times 10^6$ C. $2.34 \times 10^8$ D. $2.34 \times 10^{-8}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{80}$ ямар хоёр бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 80 ба 81 B. 8 ба 9 C. 7 ба 8 D. 9 ба 10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{30}, 6.1, 2\sqrt{10}, 4\sqrt{2}$ тоонуудыг буурах эрэмбээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $6.1, 2\sqrt{10}, 4\sqrt{2}, \sqrt{30}$ B. $2\sqrt{10}, 6.1, 4\sqrt{2}, \sqrt{30}$ C. $4\sqrt{2}, \sqrt{30}, 6.1, 2\sqrt{10}$ D. $\sqrt{30}, 4\sqrt{2}, 6.1, 2\sqrt{10}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$213.67$ тоог $0.1$ нарийвчлалтай тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 213.6 B. 213.7 C. 214 D. 213.67</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$10^{-4}$ утгыг аравтын бутархайгаар бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.001 B. 0.0001 C. 0.00001 D. 0.1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{243} \div \sqrt{3}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9 B. 81 C. 27 D. 3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$4.3465$ тоог гурван тэмдэгтээр тоймлосон нь аль вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 4.30 B. 4.34 C. 4.35 D. 4.40</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$2 \times 10^3, 2.1 \times 10^8, 7.196 \times 10^5$ өгсөн тоонуудын утгыг олоорой. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 2000, 210,000,000, 719,600 B. 200, 21,000,000, 71,960 C. 2000, 21,000,000, 719,600 D. 200, 2,100,000, 7,196</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.00048837$ тоог 1 тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.1 B. 0 C. 0.0005 D. 0.0004</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{90}$ тооны $0.1$ нарийвчлалтай ойролцоо утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.5 B. 9 C. 9.4 D. 9.48</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{42}$ ямар хоёр бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 7 ба 8 B. 6 ба 7 C. 41 ба 43 D. 5 ба 6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(2^3)^{-2}$ илэрхийллийн утгыг олно уу. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1/64 B. 64 C. 1/32 D. 32</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{320} - \sqrt{5} + \sqrt{1280}$ илэрхийллийг хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $6\sqrt{5}$ B. $\sqrt{5}$ C. $15\sqrt{5}$ D. $7\sqrt{5}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$3.7 \times 10^{11} \times 9.06 \times 10^{-4}$ үйлдлийг гүйцэтгэж, стандарт дүрсээр бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $3.35 \times 10^8$ B. $3.3522 \times 10^8$ C. $33.522 \times 10^7$ D. $3.3522 \times 10^7$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{8} + \sqrt{45}$ нийлбэрийг $0.1$ нарийвчлалтай тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 9.5 B. 9.4 C. 9.6 D. 9.3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.000000000789 = 7.89 \times 10^n$ бол $n$-ийг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. -9 B. -10 C. -11 D. -8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>$2^{3x} = 64$ бол $x$-ийг ол. 36, 51</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1 B. 2 C. 3 D. 4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{15}$ тооны $0.1$ нарийвчлалтай ойролцоо утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3.8 B. 3.9 C. 4.0 D. 3.7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.06754$ тоог хоёр тэмдэгтээр тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 0.067 B. 0.068 C. 0.07 D. 0.06</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{13^2 - 12^2}$ утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 5 B. 1 C. 25 D. $\sqrt{25}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$275.02 \times 10^{-3}$ утгыг аравтын бутархайгаар бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 2.7502 B. 0.27502 C. 27.502 D. 0.027502</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{11}$ тооны $0.1$ нарийвчлалтай ойролцоо утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3.3 B. 3 C. 4 D. 3.32</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$1.08 \times 10^6$ тоог дэлгэрэнгүй хэлбэрт бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 1,080,000 B. 108,000 C. 10,800,000 D. 1,080,000,000</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{242}$ илэрхийллийг хялбарчил. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $11\sqrt{2}$ B. $2\sqrt{11}$ C. $121\sqrt{2}$ D. $22\sqrt{2}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$29.119$ тоог $0.1$ нарийвчлалтай тоймло. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 29.1 B. 29.2 C. 29.12 D. 29.0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{128}$ илэрхийллийг $a\sqrt{b}$ дүрсэд бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $4\sqrt{8}$ B. $2\sqrt{32}$ C. $8\sqrt{2}$ D. $16\sqrt{2}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$0.000000000076$ стандарт дүрсэд бич. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. $7.6 \times 10^{-11}$ B. $7.6 \times 10^{-10}$ C. $0.76 \times 10^{-11}$ D. $76 \times 10^{-12}$</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$\sqrt{133}$ ямар хоёр бүхэл тооны хооронд орших вэ? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 10 ба 11 B. 11 ба 12 C. 12 ба 13 D. 13 ба 14</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">$(3^4 \cdot 3^5)^7 \div 27^{20}$ илэрхийллийн утгыг ол. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A. 3 B. 81 C. 1 D. 9</t>
-    </r>
-  </si>
-  <si>
     <t>B </t>
   </si>
   <si>
@@ -1444,6 +75,306 @@
   </si>
   <si>
     <t>D </t>
+  </si>
+  <si>
+    <t>$\sqrt{42}$ тоо ямар хоёр дараалсан бүхэл тооны хооронд орших вэ?A. 5 ба 6  B. 6 ба 7  C. 7 ба 8  D. 41 ба 43</t>
+  </si>
+  <si>
+    <t>$\sqrt{320} - \sqrt{5} + \sqrt{1280}$ илэрхийллийг хялбарчил.A. $25\sqrt{5}$  B. $21\sqrt{5}$  C. $23\sqrt{5}$  D. $19\sqrt{5}$</t>
+  </si>
+  <si>
+    <t>$(3^4 \cdot 3^5)^7 \div 27^{20}$ илэрхийллийн утгыг ол.A. 3  B. 9  C. 27  D. 81</t>
+  </si>
+  <si>
+    <t>$325.78$ тоог гурван тэмдэгтээр тоймло.A. 325.8  B. 326  C. 330  D. 325.7</t>
+  </si>
+  <si>
+    <t>$0.00000234$ тоог стандарт дүрсэд бич.A. $2.34 \times 10^{-6}$  B. $23.4 \times 10^{-7}$  C. $2.34 \times 10^6$  D. $2.34 \times 10^{-5}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{11}$ тооны $0.1$ нарийвчлалтай ойролцоо утгыг ол.A. 3.3  B. 3.4  C. 3.31  D. 3.32</t>
+  </si>
+  <si>
+    <t>$(\sqrt{12} - \sqrt{75} + \sqrt{48}) \cdot \frac{1}{\sqrt{3}}$ үйлдлийг гүйцэтгэ.A. 1  B. $\sqrt{3}$  C. 3  D. $\frac{1}{\sqrt{3}}$</t>
+  </si>
+  <si>
+    <t>$\frac{7}{11}$ бутархайг аравтын бутархайд шилжүүлж, үет хэсгийг ол.A. 0.63  B. 0.64  C. $0.(63)$  D. $0.(64)$</t>
+  </si>
+  <si>
+    <t>$2\sqrt{17}$ тоо ямар хоёр бүхэл тооны хооронд орших вэ?A. 7 ба 8  B. 8 ба 9  C. 9 ба 10  D. 16 ба 17</t>
+  </si>
+  <si>
+    <t>$(3.7 \times 10^{11}) \cdot (9.06 \times 10^{-4})$ үйлдлийг гүйцэтгэж, стандарт дүрсээр бич.A. $3.3522 \times 10^8$  B. $33.522 \times 10^7$  C. $3.35 \times 10^8$  D. $3.3522 \times 10^7$</t>
+  </si>
+  <si>
+    <t>$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга аль нь вэ?A. 5.9  B. 6.0  C. 5.91  D. 5.92</t>
+  </si>
+  <si>
+    <t>$\sqrt{128}$ илэрхийллийг $a\sqrt{b}$ дүрсэд оруул.A. $4\sqrt{8}$  B. $2\sqrt{32}$  C. $8\sqrt{2}$  D. $16\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$a=5.2 \times 10^7, b=4.4 \times 10^{-3}, c=3.12 \times 10^7$ тоонуудыг өсөх эрэмбээр бич.A. $a, b, c$  B. $b, c, a$  C. $c, b, a$  D. $b, a, c$</t>
+  </si>
+  <si>
+    <t>$\frac{\sqrt{8} - \sqrt{50} + \sqrt{32}}{\sqrt{8}}$ илэрхийллийг хялбарчил.A. 0.5  B. 2  C. $2\sqrt{2}$  D. 1</t>
+  </si>
+  <si>
+    <t>$\sqrt{30}, 6.1, 2\sqrt{10}, 4\sqrt{2}$ тоонуудыг буурах эрэмбээр бич.A. $2\sqrt{10}, 6.1, 4\sqrt{2}, \sqrt{30}$  B. $6.1, 2\sqrt{10}, 4\sqrt{2}, \sqrt{30}$  C. $2\sqrt{10}, 4\sqrt{2}, 6.1, \sqrt{30}$  D. $4\sqrt{2}, 2\sqrt{10}, 6.1, \sqrt{30}$</t>
+  </si>
+  <si>
+    <t>$2\sqrt{175} - 3\sqrt{28} + 2\sqrt{63}$ илэрхийллийг хялбарчил.A. $10\sqrt{7}$  B. $12\sqrt{7}$  C. $9\sqrt{7}$  D. $11\sqrt{7}$</t>
+  </si>
+  <si>
+    <t>Гэрийн шалны радиусыг метрээр тоймлоход 3 м болжээ. Талбайн авч болох хамгийн их утгыг ол.A. 28.26 м$^2$  B. 38.465 м$^2$  C. 25 м$^2$  D. 30.25 м$^2$</t>
+  </si>
+  <si>
+    <t>$0.00048837$ тоог нэг тэмдэгтээр тоймло.A. 0.0005  B. 0.0004  C. 0.00049  D. 0.001</t>
+  </si>
+  <si>
+    <t>$3^{-12} \cdot 9^5 \div (27^{-4} \cdot 9^{-2})$ утгыг ол.A. 9  B. 81  C. 243  D. 729</t>
+  </si>
+  <si>
+    <t>$\sqrt{19\frac{1}{16}}$ язгуурын утгыг ол.A. $\frac{13}{4}$  B. $\frac{17}{4}$  C. $\frac{31}{4}$  D. $\frac{19}{4}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{20} + \sqrt{45} - \sqrt{80}$ хялбарчил.A. $\sqrt{5}$  B. $2\sqrt{5}$  C. $3\sqrt{5}$  D. $5\sqrt{5}$</t>
+  </si>
+  <si>
+    <t>$120,000 \cdot 0.000002$ үржвэрийг стандарт дүрсээр бич.A. $2.4 \times 10^{-1}$  B. $2.4 \times 10^{-2}$  C. 0.24  D. $2.4 \times 10^1$</t>
+  </si>
+  <si>
+    <t>$\sqrt{8} + \sqrt{45}$ нийлбэрийг $0.1$ нарийвчлалтай тоймло.A. 9.5  B. 9.4  C. 9.6  D. 9.3</t>
+  </si>
+  <si>
+    <t>$275.02 \times 10^{-3}$ утгыг аравтын бутархайгаар бич.A. 2.7502  B. 0.27502  C. 27.502  D. 0.027502</t>
+  </si>
+  <si>
+    <t>Тэгш өнцөгтийн урт 12 см, өргөн 7 см (см-ээр тоймлосон). Талбайн авч болох хамгийн бага утга?A. 84 см$^2$  B. 74.75 см$^2$  C. 75.25 см$^2$  D. 83.25 см$^2$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{27} + 1)^2$ задалж бич.A. $28 + 6\sqrt{3}$  B. $28 + 2\sqrt{27}$  C. $29 + 4\sqrt{7}$  D. $29 + 2\sqrt{7}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{18} - 3\sqrt{8} + 2\sqrt{2}$ утгыг ол.A. $-\sqrt{2}$  B. $-2\sqrt{2}$  C. $\sqrt{2}$  D. 0</t>
+  </si>
+  <si>
+    <t>$0.06754$ тоог хоёр тэмдэгтээр тоймло.A. 0.067  B. 0.068  C. 0.07  D. 0.06</t>
+  </si>
+  <si>
+    <t>$a=3.9 \times 10^8, b=2.6 \times 10^{-5}$ бол $a \cdot b$ үржвэрийг стандарт дүрсэд бич.A. $1.014 \times 10^4$  B. $10.14 \times 10^3$  C. $1.014 \times 10^3$  D. $1.014 \times 10^2$</t>
+  </si>
+  <si>
+    <t>$\sqrt{90}$ тооны $0.01$ нарийвчлалтай илүүдэлтэй ойролцоо утга?A. 9.48  B. 9.49  C. 9.5  D. 9.47</t>
+  </si>
+  <si>
+    <t>$100 \div 10^{-3}$ утгыг 10-ын зэрэг хэлбэрт бич.A. $10^5$  B. $10^2$  C. $10^{-1}$  D. $10^6$</t>
+  </si>
+  <si>
+    <t>$\sqrt{6} + \sqrt{3}$ ерөнхий үржигдэхүүн хаалтнаас гарга.A. $3(\sqrt{2} + 1)$  B. $\sqrt{3}(\sqrt{2} + 1)$  C. $\sqrt{3}(\sqrt{2} - 1)$  D. $\sqrt{2}(\sqrt{3} + 1)$</t>
+  </si>
+  <si>
+    <t>$\sqrt{13^2 - 12^2}$ утгыг ол.A. 5  B. 1  C. 25  D. $\sqrt{25}$</t>
+  </si>
+  <si>
+    <t>$0.000000000789$ тоог $7.89 \times 10^n$ хэлбэрт бичвэл $n$ хэд вэ?A. -9  B. -10  C. -11  D. -8</t>
+  </si>
+  <si>
+    <t>$\sqrt{11}$ тооны $0.1$ нарийвчлалтай илүүдэлтэй ойролцоо утга?A. 3.3  B. 3.4  C. 3.32  D. 3.35</t>
+  </si>
+  <si>
+    <t>$5\sqrt{3} + 2\sqrt{48} - 6\sqrt{27}$ утгыг ол.A. $-5\sqrt{3}$  B. $-10\sqrt{3}$  C. $-2\sqrt{3}$  D. $-3\sqrt{3}$</t>
+  </si>
+  <si>
+    <t>$4.3465$ тоог хоёр тэмдэгтээр тоймло.A. 4.3  B. 4.4  C. 4.35  D. 4.34</t>
+  </si>
+  <si>
+    <t>$(2^3)^{-2}$ утгыг 10-тын бутархайгаар бич.A. 0.015625  B. 0.064  C. 0.15625  D. 0.0125</t>
+  </si>
+  <si>
+    <t>$\sqrt{15} - \sqrt{10}$ ерөнхий үржигдэхүүн гарга.A. $5(\sqrt{3} - \sqrt{2})$  B. $\sqrt{5}(\sqrt{3} - \sqrt{2})$  C. $\sqrt{2}(\sqrt{7.5} - 1)$  D. $\sqrt{5}(3 - 2)$</t>
+  </si>
+  <si>
+    <t>$2^{3x} = 64$ бол $x$-ийг ол.A. 1  B. 2  C. 3  D. 4</t>
+  </si>
+  <si>
+    <t>$\sqrt{900} \div \sqrt{0.09}$ утгыг ол.A. 10  B. 100  C. 30  D. 300</t>
+  </si>
+  <si>
+    <t>$1.08 \times 10^6$ тоог дэлгэрэнгүй хэлбэрт бич.A. 1,080,000  B. 108,000  C. 10,800,000  D. 1,080,000,000</t>
+  </si>
+  <si>
+    <t>$\sqrt{242}$ илэрхийллийг $11\sqrt{x}$ гэж бичсэн бол $x$ хэд вэ?A. 2  B. 3  C. 11  D. 22</t>
+  </si>
+  <si>
+    <t>$29.119$ тоог $0.1$ нарийвчлалтай тоймло.A. 29.1  B. 29.2  C. 29.12  D. 29</t>
+  </si>
+  <si>
+    <t>Гэрлийн хурд $3 \times 10^8$ м/с бол 1 минутад туулах замыг стандарт дүрсээр бич.A. $1.8 \times 10^{10}$ м  B. $18 \times 10^9$ м  C. $1.8 \times 10^9$ м  D. $1.8 \times 10^{11}$ м</t>
+  </si>
+  <si>
+    <t>$\sqrt{15}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол.A. 3.8  B. 3.9  C. 4.0  D. 3.7</t>
+  </si>
+  <si>
+    <t>$(\sqrt{128} - \sqrt{32})^2$ утгыг ол.A. 32  B. 64  C. 16  D. 8</t>
+  </si>
+  <si>
+    <t>$0.06754$ тоог нэг тэмдэгтээр тоймло.A. 0.07  B. 0.06  C. 0.1  D. 0.068</t>
+  </si>
+  <si>
+    <t>$10^{-4}$ утгыг аравтын бутархайгаар бич.A. 0.001  B. 0.0001  C. 0.00001  D. 0.1</t>
+  </si>
+  <si>
+    <t>$\sqrt{243} \div \sqrt{3}$ утгыг ол.A. 9  B. 81  C. 27  D. 3</t>
+  </si>
+  <si>
+    <t>$\sqrt{1000}$ тоо ямар хоёр бүхэл тооны хооронд орших вэ?A. 30 ба 31  B. 31 ба 32  C. 32 ба 33  D. 33 ба 34</t>
+  </si>
+  <si>
+    <t>$(\sqrt{8} + \sqrt{2})^2$ илэрхийллийн утгыг ол.A. 10  B. 12  C. 18  D. 20</t>
+  </si>
+  <si>
+    <t>$0.000000056$ тоог стандарт дүрсэд бич.A. $5.6 \times 10^{-7}$  B. $5.6 \times 10^{-8}$  C. $5.6 \times 10^{-9}$  D. $56 \times 10^{-9}$</t>
+  </si>
+  <si>
+    <t>$5.83 \times 10^4$ тоог дэлгэрэнгүй бич.A. 58,300  B. 5,830  C. 583,000  D. 5.83</t>
+  </si>
+  <si>
+    <t>$\sqrt{50} - \sqrt{18}$ хялбарчил.A. $4\sqrt{2}$  B. $2\sqrt{2}$  C. $\sqrt{2}$  D. $8\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{0.0001}$ утгыг ол.A. 0.1  B. 0.01  C. 0.001  D. 1</t>
+  </si>
+  <si>
+    <t>$(2^3 \cdot 2^2)^4 \div 2^{18}$ утгыг ол.A. 2  B. 4  C. 8  D. 16</t>
+  </si>
+  <si>
+    <t>$32000$ тоог $3.2 \times 10^n$ хэлбэрт бичвэл $n$ хэд вэ?A. 3  B. 4  C. 5  D. 6</t>
+  </si>
+  <si>
+    <t>$\sqrt{27} \cdot \sqrt{3}$ утгыг ол.A. 3  B. 9  C. 27  D. 81</t>
+  </si>
+  <si>
+    <t>$\sqrt{35}$ тооны $0.01$ нарийвчлалтай илүүдэлтэй утгыг ол.A. 5.91  B. 5.92  C. 5.9  D. 6</t>
+  </si>
+  <si>
+    <t>$\frac{1}{\sqrt{2}}$ бутархайн хуваарийг иррационалиас чөлөөл.A. $\sqrt{2}$  B. $\frac{\sqrt{2}}{2}$  C. $\frac{\sqrt{2}}{4}$  D. $2\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$8^{x} = 64$ бол $x$-ийг ол.A. 2  B. 3  C. 4  D. 8</t>
+  </si>
+  <si>
+    <t>$\sqrt{500}$ илэрхийллийг $10\sqrt{x}$ гэж бичвэл $x$ хэд вэ?A. 5  B. 50  C. 2  D. 10</t>
+  </si>
+  <si>
+    <t>$4.5678$ тоог гурван тэмдэгтээр тоймло.A. 4.56  B. 4.57  C. 4.568  D. 4.6</t>
+  </si>
+  <si>
+    <t>$10^0 \cdot 10^{-2} \cdot 10^5$ утгыг ол.A. 1,000  B. 100  C. 10  D. 1</t>
+  </si>
+  <si>
+    <t>$\sqrt{125}$ тоог $a\sqrt{b}$ хэлбэрт бич.A. $5\sqrt{5}$  B. $25\sqrt{5}$  C. $5\sqrt{25}$  D. $5\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$0.001 \times 10^6$ утгыг ол.A. 1,000  B. 10,000  C. 100  D. 1</t>
+  </si>
+  <si>
+    <t>$\sqrt{18} + \sqrt{2}$ утгыг ол.A. $3\sqrt{2}$  B. $4\sqrt{2}$  C. $5\sqrt{2}$  D. $2\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$2^{10} \div 4^4$ утгыг ол.A. 2  B. 4  C. 8  D. 16</t>
+  </si>
+  <si>
+    <t>$\sqrt{144} - \sqrt{81}$ утгыг ол.A. 3  B. 6  C. 9  D. 12</t>
+  </si>
+  <si>
+    <t>$0.00045$ тоог стандарт дүрсэд бич.A. $4.5 \times 10^{-4}$  B. $4.5 \times 10^{-3}$  C. $4.5 \times 10^{-5}$  D. $45 \times 10^{-5}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{11}$ тооны ойролцоо утгыг $0.01$ нарийвчлалтай ол.A. 3.31  B. 3.32  C. 3.3  B. 3.4</t>
+  </si>
+  <si>
+    <t>$\frac{\sqrt{50}}{\sqrt{2}}$ утгыг ол.A. 5  B. 25  C. $\sqrt{5}$  D. 10</t>
+  </si>
+  <si>
+    <t>$3^{-2} \cdot 27$ утгыг ол.A. 1  B. 3  C. 9  D. $\frac{1}{3}$</t>
+  </si>
+  <si>
+    <t>$1,234,567$ тоог хоёр тэмдэгтээр тоймло.A. 1,200,000  B. 1,230,000  C. 1,000,000  D. 1,300,000</t>
+  </si>
+  <si>
+    <t>$\sqrt{0.16} \cdot 10$ утгыг ол.A. 0.4  B. 4  C. 40  D. 1.6</t>
+  </si>
+  <si>
+    <t>$a=2.5 \times 10^{-4}$ ба $b=4 \times 10^6$ бол $a \cdot b$ утгыг ол.A. 1,000  B. 10,000  C. 100  D. 1</t>
+  </si>
+  <si>
+    <t>$\sqrt{75} - \sqrt{12}$ хялбарчил.A. $3\sqrt{3}$  B. $5\sqrt{3}$  C. $2\sqrt{3}$  D. $\sqrt{3}$</t>
+  </si>
+  <si>
+    <t>$5^{x-1} = 25$ бол $x$ хэд вэ?A. 2  B. 3  C. 4  D. 5</t>
+  </si>
+  <si>
+    <t>$\sqrt{1.21}$ утгыг ол.A. 1.1  B. 11  C. 0.11  D. 1.2</t>
+  </si>
+  <si>
+    <t>$(3^2)^3 \div 3^4$ утгыг ол.A. 3  B. 9  C. 27  D. 81</t>
+  </si>
+  <si>
+    <t>$0.00001 \div 10^{-3}$ утгыг ол.A. 0.1  B. 0.01  C. 100  D. 1,000</t>
+  </si>
+  <si>
+    <t>$\sqrt{200}$ тоо ямар хоёр бүхэл тооны хооронд орших вэ?A. 13 ба 14  B. 14 ба 15  C. 15 ба 16  D. 10 ба 11</t>
+  </si>
+  <si>
+    <t>$325.46$ тоог аравны хэсгээр тоймло.A. 325.5  B. 325.4  C. 326  D. 325.47</t>
+  </si>
+  <si>
+    <t>$\sqrt{2} \cdot \sqrt{8} \cdot \sqrt{16}$ утгыг ол.A. 4  B. 8  C. 16  D. 32</t>
+  </si>
+  <si>
+    <t>$10^{-6} \cdot 10^8$ утгыг ол.A. 0.01  B. 100  C. 1,000  D. 10</t>
+  </si>
+  <si>
+    <t>$\sqrt{x} = 7$ бол $x$ хэд вэ?A. 7  B. 14  C. 49  D. $\sqrt{7}$</t>
+  </si>
+  <si>
+    <t>$0.0000078$ тоог стандарт дүрсэд бич.A. $7.8 \times 10^{-6}$  B. $7.8 \times 10^{-5}$  C. $78 \times 10^{-7}$  D. $7.8 \times 10^6$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{3} - 1)(\sqrt{3} + 1)$ утгыг ол.A. 2  B. 4  C. $\sqrt{3}$  D. 1</t>
+  </si>
+  <si>
+    <t>$4^{3} \div 2^4$ утгыг ол.A. 2  B. 4  C. 8  D. 16</t>
+  </si>
+  <si>
+    <t>$\sqrt{98}$ тоог $a\sqrt{b}$ хэлбэрт бич.A. $7\sqrt{2}$  B. $2\sqrt{7}$  C. $49\sqrt{2}$  D. $14\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$0.12345$ тоог хоёр тэмдэгтээр тоймло.A. 0.12  B. 0.13  C. 0.1  D. 0.123</t>
+  </si>
+  <si>
+    <t>$\sqrt{10,000} \div 10^2$ утгыг ол.A. 1  B. 10  C. 100  D. 0.1</t>
+  </si>
+  <si>
+    <t>$10^{x} = 0.001$ бол $x$ хэд вэ?A. -3  B. -2  C. 3  D. 2</t>
+  </si>
+  <si>
+    <t>$\sqrt{8} + \sqrt{18} - \sqrt{50}$ утгыг ол.A. 0  B. $\sqrt{2}$  C. $2\sqrt{2}$  D. $-\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$6.7 \times 10^{-3}$ тоог аравтын бутархайгаар бич.A. 0.0067  B. 0.067  C. 0.00067  D. 0.67</t>
+  </si>
+  <si>
+    <t>$\sqrt{13^2 - 5^2}$ утгыг ол.A. 8  B. 12  C. 144  D. 18</t>
+  </si>
+  <si>
+    <t>$0.000099$ тоог нэг тэмдэгтээр тоймло.A. 0.0001  B. 0.00009  C. 0.001  D. 0.000099</t>
+  </si>
+  <si>
+    <t>$\sqrt{2} \cdot \sqrt{32}$ утгыг ол.A. 4  B. 8  C. 16  D. 64</t>
+  </si>
+  <si>
+    <t>$10^{-2} \div 10^{-5}$ утгыг ол.A. 1,000  B. 100  C. 10  D. 0.001</t>
   </si>
 </sst>
 </file>
@@ -1476,18 +407,17 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1510,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1529,13 +459,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1893,568 +826,568 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>106</v>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>8</v>
+      <c r="A3" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>106</v>
+      <c r="D3" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>106</v>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="C6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="C15" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>106</v>
+      <c r="D15" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>21</v>
+      <c r="A16" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>106</v>
+      <c r="D16" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>22</v>
+      <c r="A17" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>106</v>
+      <c r="D17" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>23</v>
+      <c r="A18" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>106</v>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>24</v>
+      <c r="A19" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>106</v>
+      <c r="D19" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>25</v>
+      <c r="A20" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>106</v>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>26</v>
+      <c r="A21" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>106</v>
+      <c r="D21" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>27</v>
+      <c r="A22" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>106</v>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>28</v>
+      <c r="A23" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>106</v>
+      <c r="D23" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>29</v>
+      <c r="A24" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>106</v>
+      <c r="D24" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>30</v>
+      <c r="A25" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>106</v>
+      <c r="D25" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>31</v>
+      <c r="A26" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>106</v>
+      <c r="D26" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>32</v>
+      <c r="A27" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>106</v>
+      <c r="D27" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>33</v>
+      <c r="A28" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>106</v>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>34</v>
+      <c r="A29" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>106</v>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>35</v>
+      <c r="A30" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>106</v>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>36</v>
+      <c r="A31" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>106</v>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>37</v>
+      <c r="A32" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>106</v>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>38</v>
+      <c r="A33" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>106</v>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>39</v>
+      <c r="A34" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>106</v>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>40</v>
+      <c r="A35" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>106</v>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>41</v>
+      <c r="A36" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>106</v>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>42</v>
+      <c r="A37" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="8" t="s">
-        <v>106</v>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>43</v>
+      <c r="A38" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>106</v>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>44</v>
+      <c r="A39" s="9" t="s">
+        <v>49</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>106</v>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>45</v>
+      <c r="A40" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>106</v>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>46</v>
+      <c r="A41" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>106</v>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
-        <v>47</v>
+      <c r="A42" s="9" t="s">
+        <v>52</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>5</v>
@@ -2462,433 +1395,433 @@
       <c r="C42" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>106</v>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>48</v>
+      <c r="A43" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>106</v>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>49</v>
+      <c r="A44" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>106</v>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>50</v>
+      <c r="A45" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>106</v>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>51</v>
+      <c r="A46" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="8" t="s">
-        <v>106</v>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>52</v>
+      <c r="A47" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="8" t="s">
-        <v>106</v>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>53</v>
+      <c r="A48" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D48" s="8" t="s">
-        <v>106</v>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>54</v>
+      <c r="A49" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>106</v>
+      <c r="D49" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
-        <v>55</v>
+      <c r="A50" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>106</v>
+      <c r="D50" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>56</v>
+      <c r="A51" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>106</v>
+      <c r="D51" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
-        <v>57</v>
+      <c r="A52" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>106</v>
+      <c r="D52" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>58</v>
+      <c r="A53" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D53" s="8" t="s">
-        <v>106</v>
+      <c r="D53" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="7" t="s">
-        <v>59</v>
+      <c r="A54" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="8" t="s">
-        <v>106</v>
+      <c r="D54" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="7" t="s">
-        <v>60</v>
+      <c r="A55" s="9" t="s">
+        <v>65</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="8" t="s">
-        <v>106</v>
+      <c r="D55" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="7" t="s">
-        <v>61</v>
+      <c r="A56" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="8" t="s">
-        <v>106</v>
+      <c r="D56" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
-        <v>62</v>
+      <c r="A57" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>106</v>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="7" t="s">
-        <v>63</v>
+      <c r="A58" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="8" t="s">
-        <v>106</v>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="7" t="s">
-        <v>64</v>
+      <c r="A59" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="8" t="s">
-        <v>106</v>
+      <c r="D59" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="7" t="s">
-        <v>65</v>
+      <c r="A60" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>106</v>
+      <c r="D60" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="7" t="s">
-        <v>66</v>
+      <c r="A61" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="8" t="s">
-        <v>106</v>
+      <c r="D61" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
-        <v>67</v>
+      <c r="A62" s="9" t="s">
+        <v>72</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="8" t="s">
-        <v>106</v>
+      <c r="D62" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
-        <v>68</v>
+      <c r="A63" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="8" t="s">
-        <v>106</v>
+      <c r="D63" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
-        <v>69</v>
+      <c r="A64" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="8" t="s">
-        <v>106</v>
+      <c r="D64" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
-        <v>70</v>
+      <c r="A65" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>106</v>
+      <c r="D65" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
-        <v>71</v>
+      <c r="A66" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="8" t="s">
-        <v>106</v>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>72</v>
+      <c r="A67" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>106</v>
+      <c r="D67" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="7" t="s">
-        <v>73</v>
+      <c r="A68" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="8" t="s">
-        <v>106</v>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="7" t="s">
-        <v>74</v>
+      <c r="A69" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>106</v>
+      <c r="D69" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="7" t="s">
-        <v>75</v>
+      <c r="A70" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>109</v>
+        <v>11</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>106</v>
+      <c r="D70" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" s="9" t="s">
+      <c r="A71" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>106</v>
+      <c r="D71" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="7" t="s">
-        <v>77</v>
+      <c r="A72" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>106</v>
+      <c r="D72" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
-        <v>78</v>
+      <c r="A73" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>6</v>
@@ -2896,403 +1829,404 @@
       <c r="C73" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="9" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="4" t="s">
+      <c r="B96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C76" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B79" s="4" t="s">
+      <c r="B97" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D86" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D90" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D93" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="B99" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="8" t="s">
-        <v>106</v>
+      <c r="D99" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="7" t="s">
-        <v>74</v>
+      <c r="A100" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="8" t="s">
-        <v>106</v>
+      <c r="D100" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="7" t="s">
-        <v>72</v>
+      <c r="A101" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="8" t="s">
-        <v>106</v>
+      <c r="D101" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="10"/>
       <c r="B102" s="5"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
